--- a/sheets/대금율보/검수/대금산조 진양.xlsx
+++ b/sheets/대금율보/검수/대금산조 진양.xlsx
@@ -5283,7 +5283,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 淋
 –</t>
         </is>
@@ -5292,14 +5292,14 @@
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林フ
-林?
+林
 南)</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 △
 淋</t>
         </is>
@@ -5445,7 +5445,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 湳)
 –</t>
         </is>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 南)
 –</t>
         </is>
@@ -5613,7 +5613,7 @@
       <c r="M7" s="24"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?
+          <t xml:space="preserve">汰
 汰
 –潢</t>
         </is>
@@ -5770,7 +5770,7 @@
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南?
+          <t xml:space="preserve">南
 南
 –</t>
         </is>
@@ -5792,15 +5792,15 @@
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 △
-汰?</t>
+汰</t>
         </is>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?
+          <t xml:space="preserve">汰
 汰
 –</t>
         </is>
@@ -5839,7 +5839,7 @@
       <c r="C12" s="24"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?
+          <t xml:space="preserve">仲
 南汰
 南)</t>
         </is>
@@ -5960,7 +5960,7 @@
         <is>
           <t xml:space="preserve">林
 仲
-仲?</t>
+仲</t>
         </is>
       </c>
       <c r="M13" s="22"/>
@@ -6029,7 +6029,7 @@
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢?</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="O14" s="22" t="inlineStr">
@@ -6137,7 +6137,7 @@
         <is>
           <t xml:space="preserve">林仲
 –
-仲?</t>
+仲</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="T21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 汰
 –</t>
         </is>
@@ -6438,7 +6438,7 @@
       <c r="N23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-淋?
+淋
 –</t>
         </is>
       </c>
@@ -6450,7 +6450,7 @@
       <c r="P23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-林?
+林
 –</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/대금산조 진양.xlsx
+++ b/sheets/대금율보/검수/대금산조 진양.xlsx
@@ -5227,32 +5227,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="15.29" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="305.98" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="U3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="305.98" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="U4" s="24"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="305.98" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="305.98" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       <c r="T6" s="23"/>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="305.98" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23"/>
       <c r="C7" s="24"/>
@@ -5630,7 +5630,7 @@
       <c r="T7" s="23"/>
       <c r="U7" s="24"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="305.98" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -5720,10 +5720,10 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9">
+    <row r="9" ht="6.0" customHeight="true">
       <c r="A9" s="0"/>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="102.56" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="20" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
       <c r="T10" s="20"/>
       <c r="U10" s="20"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="305.98" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="305.98" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="U12" s="24"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="305.98" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="U13" s="24"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="305.98" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
       <c r="T14" s="23"/>
       <c r="U14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="305.98" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="23"/>
       <c r="C15" s="24"/>
@@ -6089,7 +6089,7 @@
       <c r="T15" s="23"/>
       <c r="U15" s="24"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="305.98" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
@@ -6176,10 +6176,10 @@
       </c>
       <c r="U16" s="24"/>
     </row>
-    <row r="17">
+    <row r="17" ht="6.0" customHeight="true">
       <c r="A17" s="0"/>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="102.56" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="20" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       <c r="T18" s="20"/>
       <c r="U18" s="20"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="305.98" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="23"/>
       <c r="C19" s="24"/>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="U19" s="24"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="305.98" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="23"/>
       <c r="C20" s="24"/>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="U20" s="24"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="305.98" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="23"/>
       <c r="C21" s="24"/>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="305.98" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="23"/>
       <c r="C22" s="24"/>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="U22" s="24"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="305.98" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="23"/>
       <c r="C23" s="24"/>
@@ -6470,7 +6470,7 @@
       <c r="T23" s="23"/>
       <c r="U23" s="24"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="305.98" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="23"/>
       <c r="C24" s="24"/>
@@ -6533,7 +6533,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="8" max="16383" man="1"/>
     <brk id="16" max="16383" man="1"/>
